--- a/src/attributions/attributions_ig_traj_329.xlsx
+++ b/src/attributions/attributions_ig_traj_329.xlsx
@@ -1002,61 +1002,61 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.006724027397604539</v>
+        <v>0.04498175443757646</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.003801982469032516</v>
+        <v>0.04031770053391959</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.491301089076003e-12</v>
+        <v>-8.48605762470103e-11</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.003873511809529917</v>
+        <v>-0.04638545838848948</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001997882553739604</v>
+        <v>-0.04049932453240818</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01906790465420848</v>
+        <v>0.1818141354729018</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.089992795627616e-13</v>
+        <v>-4.03868340995727e-11</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1065,70 +1065,70 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-6.690912427983522e-12</v>
+        <v>-7.0783421097198e-11</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.098435541410004e-12</v>
+        <v>-5.165212740296072e-11</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB2" t="n">
         <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.006927682631248281</v>
+        <v>-0.10317587041801</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.001604107402440182</v>
+        <v>-0.07502499602276735</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.001620244548587141</v>
+        <v>-0.1056560892263373</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.003546879001023009</v>
+        <v>-0.008920613979478234</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.007308005163129001</v>
+        <v>-0.03861902786877779</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.005834901014873043</v>
+        <v>-0.09011703884578619</v>
       </c>
       <c r="AQ2" t="n">
         <v>-0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
@@ -1137,76 +1137,76 @@
         <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.01609913842861809</v>
+        <v>0.3577008854889728</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.01246793039258798</v>
+        <v>0.0408253959971684</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0.01962612935328174</v>
+        <v>-0.04119173840671859</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.573356867461098e-12</v>
+        <v>-3.136416798599776e-11</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-5.514155323085858e-12</v>
+        <v>-9.727734956198809e-12</v>
       </c>
       <c r="BH2" t="n">
-        <v>-2.206328511376905e-12</v>
+        <v>-6.837631482687195e-11</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.003803541537365842</v>
+        <v>0.07893873421578827</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.003951363781171237</v>
+        <v>0.09718517978126154</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.006045566946613047</v>
+        <v>0.09714202196192608</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
         <v>-0</v>
@@ -1218,19 +1218,19 @@
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.007724513509624044</v>
+        <v>0.09640295433537698</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
         <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.01172315691892767</v>
+        <v>-0.03701188013718234</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.006395055188156556</v>
+        <v>-0.1737189948666385</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
@@ -1245,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.002208430811748141</v>
+        <v>-0.02306931804539164</v>
       </c>
       <c r="CF2" t="n">
         <v>-0</v>
@@ -1254,37 +1254,37 @@
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.003108390128135686</v>
+        <v>-0.0506174605444001</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.01117930598438167</v>
+        <v>0.09428129366627327</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.01053190225256862</v>
+        <v>-0.06662778845178692</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.01314856734536846</v>
+        <v>0.01688797494156396</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.003685322708582333</v>
+        <v>0.07111496574511933</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
@@ -1293,13 +1293,13 @@
         <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.001010739301790299</v>
+        <v>-0.03611187884992939</v>
       </c>
       <c r="CX2" t="n">
         <v>0</v>
@@ -1308,13 +1308,13 @@
         <v>-0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.003225385559528425</v>
+        <v>-0.06568146979558497</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.01395246711602404</v>
+        <v>0.07550691248396108</v>
       </c>
       <c r="DB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC2" t="n">
         <v>0</v>
@@ -1323,10 +1323,10 @@
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.001778038970123845</v>
+        <v>-0.01208991985007899</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
@@ -1335,10 +1335,10 @@
         <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.02962215814039919</v>
+        <v>-0.03680616398756555</v>
       </c>
       <c r="DJ2" t="n">
-        <v>-0.001894671255332112</v>
+        <v>0.006181873463552096</v>
       </c>
       <c r="DK2" t="n">
         <v>0</v>
@@ -1347,13 +1347,13 @@
         <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.004874561626962782</v>
+        <v>-0.01351646935037037</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
@@ -1362,25 +1362,25 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.01962582461764723</v>
+        <v>0.08113468070545475</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0.002851777583811409</v>
+        <v>0.1551739799915098</v>
       </c>
       <c r="DT2" t="n">
         <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW2" t="n">
         <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.01054485850167334</v>
+        <v>0.02034786334620779</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
@@ -1389,16 +1389,16 @@
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.009352019471799334</v>
+        <v>-0.02088343013710773</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.0002998103058905203</v>
+        <v>0.07802893924762865</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
         <v>-0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.00174078480718735</v>
+        <v>-0.03983021776900888</v>
       </c>
       <c r="EH2" t="n">
         <v>-0</v>
@@ -1416,43 +1416,43 @@
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.01259892706350614</v>
+        <v>-0.1022160707649136</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.01653776074619934</v>
+        <v>-0.02440948362963526</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.001636239476928675</v>
+        <v>0.006323697002119608</v>
       </c>
       <c r="EQ2" t="n">
         <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.007467030225624551</v>
+        <v>-0.03499578911994336</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.006153432538030631</v>
+        <v>0.02908663289621046</v>
       </c>
       <c r="EU2" t="n">
         <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>-0</v>
@@ -1461,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.001802478304296327</v>
+        <v>-0.04656898322975671</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
@@ -1470,13 +1470,13 @@
         <v>0</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.004517300084448173</v>
+        <v>-0.07899865268218575</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.01289646563372018</v>
+        <v>0.07352261356617917</v>
       </c>
       <c r="FD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE2" t="n">
         <v>-0</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.001282534456187125</v>
+        <v>0.08475765156393229</v>
       </c>
       <c r="FI2" t="n">
         <v>0</v>
@@ -1497,37 +1497,37 @@
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.01207198324223689</v>
+        <v>0.09011935140548212</v>
       </c>
       <c r="FL2" t="n">
-        <v>-0.008005867810044792</v>
+        <v>-0.02480555939709772</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.01209293919398212</v>
+        <v>-0.1368300474513034</v>
       </c>
       <c r="FR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS2" t="n">
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.005791469097469412</v>
+        <v>-0.2156722995949855</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0.001324234899053263</v>
+        <v>-0.001105052501302235</v>
       </c>
       <c r="FV2" t="n">
         <v>-0</v>
@@ -1542,19 +1542,19 @@
         <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.004384923403729583</v>
+        <v>0.01233159508432815</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
         <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.003853923101983149</v>
+        <v>0.02326312666464803</v>
       </c>
       <c r="GE2" t="n">
         <v>0</v>
@@ -1563,87 +1563,87 @@
         <v>0</v>
       </c>
       <c r="GG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01494480458863086</v>
+        <v>0.03099838622079315</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04260062785670078</v>
+        <v>0.06215826956156558</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01682434280639366</v>
+        <v>-0.0148622933939545</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05946074294903989</v>
+        <v>0.1288937720949951</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.007749311510888104</v>
+        <v>-0.01862763455972674</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.01238183580083702</v>
+        <v>0.001275688712792705</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.005501887871422029</v>
+        <v>0.009737315385256469</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.003880481013597704</v>
+        <v>-0.002395640021689428</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.877555168838153e-11</v>
+        <v>4.677257356580086e-12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>-0</v>
@@ -1652,22 +1652,22 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.02327312900022703</v>
+        <v>0.01150049845432372</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.01349658270789232</v>
+        <v>0.09121835130632028</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.01118615247118286</v>
+        <v>-0.06700313724219409</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI3" t="n">
         <v>-0</v>
@@ -1676,19 +1676,19 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.006490768839420522</v>
+        <v>-0.08805348484422397</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.04345112197744692</v>
+        <v>0.01380154541460303</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.01670314853453777</v>
+        <v>-0.1328763886791613</v>
       </c>
       <c r="AP3" t="n">
         <v>-0</v>
@@ -1706,25 +1706,25 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.1490150574230973</v>
+        <v>-0.2050045061179183</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.04286404394074164</v>
+        <v>0.09894535874325835</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.1267345527526358</v>
+        <v>0.001084771527835306</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
@@ -1733,16 +1733,16 @@
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.01586466430009856</v>
+        <v>0.03211174341571712</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.002922693457990223</v>
+        <v>-0.001946775753489389</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.293301305246495e-11</v>
+        <v>-2.190592283567753e-11</v>
       </c>
       <c r="BH3" t="n">
         <v>-0</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
         <v>-0</v>
@@ -1760,16 +1760,16 @@
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.0577061969225619</v>
+        <v>0.03982167277533567</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.02035617100413167</v>
+        <v>0.03874193474556038</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.06941695018212221</v>
+        <v>0.03470096066288404</v>
       </c>
       <c r="BQ3" t="n">
         <v>-0</v>
@@ -1787,19 +1787,19 @@
         <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.06260749076226829</v>
+        <v>-0.1495463993188566</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.005758584710078334</v>
+        <v>0.06067776910031113</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.06049244271729702</v>
+        <v>-0.05047403785738307</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA3" t="n">
         <v>0</v>
@@ -1808,31 +1808,31 @@
         <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.03122090629173501</v>
+        <v>0.09728977691664516</v>
       </c>
       <c r="CF3" t="n">
         <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.01003046807321934</v>
+        <v>-0.06279237771615119</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.008601585871208137</v>
+        <v>0.001180267242909145</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
         <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
         <v>0</v>
@@ -1841,19 +1841,19 @@
         <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.007065238529465951</v>
+        <v>0.110374963248056</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.06223538254327724</v>
+        <v>-0.02597664840301647</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.1479509723313149</v>
+        <v>0.05074124086224135</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
@@ -1862,25 +1862,25 @@
         <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV3" t="n">
         <v>-0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.03769638480913138</v>
+        <v>0.1047525791648673</v>
       </c>
       <c r="CX3" t="n">
         <v>-0</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.01892767790793748</v>
+        <v>-0.06845502861173892</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.005460283673775407</v>
+        <v>0.001752589812292356</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB3" t="n">
         <v>-0</v>
@@ -1895,49 +1895,49 @@
         <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.0006173351787545912</v>
+        <v>0.1518673971179966</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.0124051038919533</v>
+        <v>-0.02512761778421828</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.0188479585421033</v>
+        <v>0.01513056469287793</v>
       </c>
       <c r="DJ3" t="n">
         <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL3" t="n">
         <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.003766345620859322</v>
+        <v>0.03447439496250471</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.05367586797839227</v>
+        <v>-0.04075164111852579</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.02089003234863019</v>
+        <v>0.007202672083200608</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
@@ -1946,28 +1946,28 @@
         <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.0237065243743631</v>
+        <v>0.05054874096579776</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-0.01260722080282868</v>
+        <v>0.002906752724365419</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.03850191676859504</v>
+        <v>0.007703208132574054</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
         <v>0</v>
@@ -1976,49 +1976,49 @@
         <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.01507256963883279</v>
+        <v>0.0948731741780055</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0.002948708856904825</v>
+        <v>-0.06904563438149816</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.05468613206758979</v>
+        <v>-0.0169156352130102</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.05188282688126965</v>
+        <v>0.07293597967871192</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0.03575714124643788</v>
+        <v>-0.03119124449843577</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.0008772414958131187</v>
+        <v>0.03362415228885041</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
         <v>-0</v>
@@ -2027,22 +2027,22 @@
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.03718788315381553</v>
+        <v>0.104854292364995</v>
       </c>
       <c r="EZ3" t="n">
         <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>-0.008666313619122189</v>
+        <v>-0.0702640046118838</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.01514022172920947</v>
+        <v>0.009115386238240392</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
@@ -2054,76 +2054,76 @@
         <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.02390108763374509</v>
+        <v>-0.01852579706709384</v>
       </c>
       <c r="FI3" t="n">
         <v>0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>-0.04057320533823214</v>
+        <v>-0.04041592783140677</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.02235906425324091</v>
+        <v>-0.01350062964496622</v>
       </c>
       <c r="FL3" t="n">
         <v>0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP3" t="n">
         <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.04446933383967731</v>
+        <v>0.1157027096115647</v>
       </c>
       <c r="FR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.02725731579964978</v>
+        <v>0.08000997032222901</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.05863873252439428</v>
+        <v>0.04325610157128299</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
         <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
         <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.02280089831780853</v>
+        <v>0.1177914000054319</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.009983796420034101</v>
+        <v>-0.05284695197504332</v>
       </c>
       <c r="GC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03919468074931017</v>
+        <v>0.03084489060021621</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01547986419447986</v>
+        <v>-0.003385088753771394</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2161,13 +2161,13 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009210267402255097</v>
+        <v>0.003837567400245186</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.00219520691896103</v>
+        <v>-0.00415688697432781</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0002902132623002688</v>
+        <v>0.001329493951429654</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2185,52 +2185,52 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02686048953818593</v>
+        <v>0.001142904787455136</v>
       </c>
       <c r="S4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0017045605693939</v>
+        <v>-0.002128457378177222</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0006450896043324879</v>
+        <v>-0.003460301479453056</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
         <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0006482504858728567</v>
+        <v>0.000624080503279937</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01725170151535363</v>
+        <v>-0.01436248071531152</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0149555010023618</v>
+        <v>-0.01506790474159023</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -2239,16 +2239,16 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0180144010494598</v>
+        <v>0.0006672757083480097</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01571482056737866</v>
+        <v>0.02491491006185038</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,37 +2257,37 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01378582864115066</v>
+        <v>-0.002144806333229222</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0.01464339083816128</v>
+        <v>-0.01261169943814565</v>
       </c>
       <c r="AT4" t="n">
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1318926999934933</v>
+        <v>0.100590059857697</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.07881906676914228</v>
+        <v>-0.01915867826216227</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2296,13 +2296,13 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.001587449560533985</v>
+        <v>0.0129386872701549</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.001760777744056896</v>
+        <v>-0.001097704466461575</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,25 +2311,25 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.002314197789616046</v>
+        <v>-0.001371108733307421</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.02896324037906408</v>
+        <v>0.02395714762875439</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0005080843210352728</v>
+        <v>0.01746221244323018</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
@@ -2338,52 +2338,52 @@
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.04226170535306503</v>
+        <v>0.03806157675618494</v>
       </c>
       <c r="BQ4" t="n">
         <v>-0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.02607047399336422</v>
+        <v>0.01236015409810282</v>
       </c>
       <c r="BU4" t="n">
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0478393792267295</v>
+        <v>0.04916254991336483</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.02649933213642525</v>
+        <v>-0.0164145100822003</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.01268734059029185</v>
+        <v>-0.01406726635399896</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.01390634455742007</v>
+        <v>-0.0202022677640853</v>
       </c>
       <c r="CF4" t="n">
         <v>-0</v>
@@ -2392,7 +2392,7 @@
         <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.007393818278409464</v>
+        <v>-0.003219691651850837</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
@@ -2404,22 +2404,22 @@
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.01744220821586703</v>
+        <v>0.01016739421974043</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.005069944978896601</v>
+        <v>-0.0316569078886774</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.004299834234916242</v>
+        <v>0.00353312513416043</v>
       </c>
       <c r="CR4" t="n">
         <v>-0</v>
@@ -2431,22 +2431,22 @@
         <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>-0.002610799543212085</v>
+        <v>0.02891476091223247</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.01185769174042145</v>
+        <v>-0.02095673029624973</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.004860737341540623</v>
+        <v>-0.002956123419399684</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
@@ -2458,148 +2458,148 @@
         <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.01772398236214692</v>
+        <v>0.008303122440720311</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.03224759629648891</v>
+        <v>-0.009689961672314456</v>
       </c>
       <c r="DG4" t="n">
         <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.03360032483698504</v>
+        <v>-0.01305470345199164</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>-0.0032341904447024</v>
+        <v>-0.001490206849197601</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.0009499992191781636</v>
+        <v>-0.02013001606726236</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.003451901895626702</v>
+        <v>0.001168935273081138</v>
       </c>
       <c r="DS4" t="n">
         <v>-0</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0.007235803824694889</v>
+        <v>-0.02402915862546311</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.007709472411541623</v>
+        <v>0.015053639451441</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.00407705085837197</v>
+        <v>-0.005481959748135563</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>-0.01024856545326061</v>
+        <v>-0.002292700565617119</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.004215743433920147</v>
+        <v>-0.01730816527639912</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI4" t="n">
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.001440960362568181</v>
+        <v>-0.01012028422567201</v>
       </c>
       <c r="EK4" t="n">
         <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.02470757216789808</v>
+        <v>0.00398068717098214</v>
       </c>
       <c r="EO4" t="n">
         <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.0422057010959366</v>
+        <v>0.005499614579380603</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.00262565850687477</v>
+        <v>-0.00328899531747761</v>
       </c>
       <c r="ET4" t="n">
         <v>-0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.009939383187204701</v>
+        <v>0.00684801262293712</v>
       </c>
       <c r="EX4" t="n">
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.01910132180486955</v>
+        <v>-0.02422921088327266</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,7 +2608,7 @@
         <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.002676790601548233</v>
+        <v>-0.01032026211179874</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
@@ -2620,49 +2620,49 @@
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.01143680882526962</v>
+        <v>0.009993728353990807</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.004092917541881958</v>
+        <v>-0.01220821425386241</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01707909593968408</v>
+        <v>-0.003442649454486574</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.005442860281002179</v>
+        <v>0.03799451652890638</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.03732099111666496</v>
+        <v>0.007350992400376373</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.01653156573766042</v>
+        <v>-0.009699116184481642</v>
       </c>
       <c r="FU4" t="n">
         <v>-0</v>
@@ -2671,19 +2671,19 @@
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.0006235150334268566</v>
+        <v>0.001701595315279085</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.03334894539099834</v>
+        <v>-0.00849549197244286</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
@@ -2692,16 +2692,16 @@
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.01434756470511656</v>
+        <v>-0.0005457799456035636</v>
       </c>
     </row>
     <row r="5">
@@ -3278,22 +3278,22 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2496662987834158</v>
+        <v>0.1812321995193031</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1003615423477135</v>
+        <v>-0.1265136602219386</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.005288236973213054</v>
+        <v>0.0793985715558401</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
         <v>-0</v>
@@ -3305,43 +3305,43 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01273280390469787</v>
+        <v>0.01417371439535675</v>
       </c>
       <c r="L6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05615744433080609</v>
+        <v>0.09906983758372348</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0007788682065893336</v>
+        <v>-0.001423567593868899</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S6" t="n">
         <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0159452625302905</v>
+        <v>0.0353420506910867</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.01437653128287097</v>
+        <v>-0.004472630371546473</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.01734701299389794</v>
+        <v>-0.003255427456324032</v>
       </c>
       <c r="X6" t="n">
         <v>-0</v>
@@ -3350,7 +3350,7 @@
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -3359,43 +3359,43 @@
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.07820423440874827</v>
+        <v>0.03255056919707309</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.004615013793487137</v>
+        <v>-0.07783358841629889</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.03470274265326472</v>
+        <v>-0.1654110790303226</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.06537130652677167</v>
+        <v>0.158469386248913</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.06420466417008622</v>
+        <v>-0.1131268860166304</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.09192680736985287</v>
+        <v>0.1177566795678505</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
@@ -3404,52 +3404,52 @@
         <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.4845478253752625</v>
+        <v>0.3390439277709584</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.06288966802730714</v>
+        <v>-0.2480683530365116</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1941068278289766</v>
+        <v>-0.1291060202248058</v>
       </c>
       <c r="AY6" t="n">
         <v>-0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.006880014131239389</v>
+        <v>-0.0103527855722659</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.006758338516098154</v>
+        <v>0.002847924313178938</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.01885676104710685</v>
+        <v>0.00652392266849596</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -3458,31 +3458,31 @@
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.04373648070606284</v>
+        <v>0.02946948528928751</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.04845785738788445</v>
+        <v>0.05284398523598167</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1138329199514016</v>
+        <v>-0.02392821010435692</v>
       </c>
       <c r="BQ6" t="n">
         <v>-0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3494,22 +3494,22 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.2472530556075988</v>
+        <v>0.2650889420081063</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.07997965590366114</v>
+        <v>-0.2794091087391373</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.02746492935523543</v>
+        <v>0.06765113893257366</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>-0</v>
@@ -3521,130 +3521,130 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.08093070669787564</v>
+        <v>-0.08887574225001744</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.03027383997515347</v>
+        <v>0.1984999674356797</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.03017411977009676</v>
+        <v>-0.100273785927783</v>
       </c>
       <c r="CI6" t="n">
         <v>-0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.05656024621151123</v>
+        <v>-0.1291288883806562</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.1216791586154462</v>
+        <v>0.2323012492360914</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.1796305460432978</v>
+        <v>-0.006356251944424144</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.0804752561047216</v>
+        <v>-0.1004287727635244</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.06331746451548649</v>
+        <v>0.1958299833984683</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.004417027553799506</v>
+        <v>-0.08306822129314238</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.01166402768660995</v>
+        <v>-0.01797920032932421</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.06359612793841739</v>
+        <v>0.08956833375755435</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.05382924665225017</v>
+        <v>-0.1252888252863736</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.05094885539223424</v>
+        <v>-0.08267718391803684</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.01263402601765664</v>
+        <v>0.07703588828609005</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.03429267319327076</v>
+        <v>-0.09939370869423499</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
         <v>-0</v>
@@ -3653,52 +3653,52 @@
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0456530920674928</v>
+        <v>0.03351273282322693</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.04706618842161064</v>
+        <v>0.07419561430855651</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.009888167829144883</v>
+        <v>-0.04650614008429329</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.03048769131324683</v>
+        <v>-0.00696170826174055</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.062609859092931</v>
+        <v>0.17842466261109</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.015365191815184</v>
+        <v>-0.05698144136240119</v>
       </c>
       <c r="EK6" t="n">
         <v>-0</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>-0</v>
@@ -3707,28 +3707,28 @@
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.09585586915928634</v>
+        <v>-0.07001146982888933</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0.07628789869352054</v>
+        <v>-0.17036352065722</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.07668287521740445</v>
+        <v>-0.08197086918395248</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
         <v>-0</v>
@@ -3737,43 +3737,43 @@
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.08628527956258754</v>
+        <v>-0.1147671248057587</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.05262514034641411</v>
+        <v>0.2231361539365033</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.02378939893446546</v>
+        <v>-0.09345013001051268</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.001891045609774924</v>
+        <v>-0.03900464334623726</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.04118545316800837</v>
+        <v>0.05963927254503608</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0536594239929019</v>
+        <v>-0.08959585150912773</v>
       </c>
       <c r="FL6" t="n">
         <v>-0</v>
@@ -3785,28 +3785,28 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.04757545541819704</v>
+        <v>0.02860210089095343</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.008791926860107926</v>
+        <v>0.1736119289712142</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.06501622239565893</v>
+        <v>-0.04446685007817731</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
         <v>0</v>
@@ -3815,31 +3815,31 @@
         <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.03816996224628663</v>
+        <v>-0.05960278387420351</v>
       </c>
       <c r="GA6" t="n">
         <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.01331582104559085</v>
+        <v>0.1563856821367013</v>
       </c>
       <c r="GC6" t="n">
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1299859523310019</v>
+        <v>0.131666333322253</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.02940221668283416</v>
+        <v>-0.04357958207268802</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04137914807006387</v>
+        <v>-0.03456681947765893</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0005796213257499482</v>
+        <v>-0.005477593100032079</v>
       </c>
       <c r="I7" t="n">
         <v>-0</v>
@@ -3874,16 +3874,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02473438098828509</v>
+        <v>0.03228147136287386</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02974517772818213</v>
+        <v>0.05233941806509995</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.004831968555983041</v>
+        <v>-0.004027342101337834</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.01192302472268048</v>
+        <v>0.008370024143095747</v>
       </c>
       <c r="R7" t="n">
         <v>-0</v>
@@ -3901,43 +3901,43 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03563876976340338</v>
+        <v>0.03337379642373989</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.009068289392355712</v>
+        <v>-0.02030883535134177</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.001557508092338095</v>
+        <v>-0.02944575215523152</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.002274844033983848</v>
+        <v>0.007369294947304685</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.01594024658204436</v>
+        <v>-0.01004446600621062</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.06278396585439215</v>
+        <v>-0.07264839289007469</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.01325758240849093</v>
+        <v>-0.07379491889672767</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,7 +3946,7 @@
         <v>-0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.01270611205781918</v>
+        <v>0.01740811398448022</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -3955,16 +3955,16 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.01044871183951657</v>
+        <v>0.08802267590513924</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.03027375584694591</v>
+        <v>-0.01297412110029881</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.06488359956318754</v>
+        <v>0.042724652490898</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3973,34 +3973,34 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.004607216136237265</v>
+        <v>-0.01822197877752831</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.2897292584345153</v>
+        <v>0.2153229068296278</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.04608358671053553</v>
+        <v>-0.04793774931041139</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.129943941306313</v>
+        <v>-0.1519088100446084</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
         <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.03989485887910153</v>
+        <v>-0.03477196985754659</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
@@ -4009,16 +4009,16 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.00274145882222404</v>
+        <v>-0.002590703619840462</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.009628114584268006</v>
+        <v>-0.01653974070149705</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.05582740358318073</v>
+        <v>-0.002526024365478529</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.007922381404545925</v>
+        <v>-0.01751994942891587</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,25 +4036,25 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.09582919485546577</v>
+        <v>0.03613864746021042</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.1017776293496123</v>
+        <v>0.0357047504605854</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.05621429304300584</v>
+        <v>0.05195891077127154</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.05405955028957849</v>
+        <v>0.01587429391652213</v>
       </c>
       <c r="BT7" t="n">
         <v>-0</v>
@@ -4063,97 +4063,97 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1542170621213159</v>
+        <v>0.1508011012496254</v>
       </c>
       <c r="BW7" t="n">
         <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.02784005005144844</v>
+        <v>-0.05182686378498259</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.02197638297586751</v>
+        <v>-0.09425243261663137</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.01514588747280373</v>
+        <v>-0.0502677092756174</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.04711721478308185</v>
+        <v>-0.06694379604507626</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.01367311833079761</v>
+        <v>0.05188647660821531</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.01405360458545685</v>
+        <v>0.01112136603263673</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.01187751714603649</v>
+        <v>-0.005491958872937359</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.04945312653927172</v>
+        <v>-0.07153762970428929</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.07017153526788257</v>
+        <v>0.07928852774562083</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.03287123134753681</v>
+        <v>0.09563960919633285</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.04842079904828514</v>
+        <v>0.02006683570813825</v>
       </c>
       <c r="CU7" t="n">
         <v>0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.02806956239398626</v>
+        <v>-0.07066522332808647</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.03369932674717268</v>
+        <v>0.06160264919298494</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.01839254933341269</v>
+        <v>0.02340339734482618</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
@@ -4162,34 +4162,34 @@
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.01490839582406044</v>
+        <v>-0.008987586472411897</v>
       </c>
       <c r="DD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.04654185973764197</v>
+        <v>-0.0544516824071089</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.01855124102527658</v>
+        <v>0.02438397523967112</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.005762721834932603</v>
+        <v>-0.01445733989354715</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.007264052902888819</v>
+        <v>-0.008459766423528562</v>
       </c>
       <c r="DM7" t="n">
         <v>-0</v>
@@ -4198,70 +4198,70 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.07329776077411788</v>
+        <v>-0.06262190941767262</v>
       </c>
       <c r="DP7" t="n">
         <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.01102592315871934</v>
+        <v>0.03386766107397124</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.05577409620299251</v>
+        <v>-0.05707071871415709</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0.05973494753121723</v>
+        <v>0.05626649737189451</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.02158476758015909</v>
+        <v>0.08118226020110293</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.01985554037821216</v>
+        <v>0.0682116115850752</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.01828009527514125</v>
+        <v>-0.03798153204754089</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.007163942619161775</v>
+        <v>0.07511966701198318</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.02703318998370449</v>
+        <v>-0.02298330171708018</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.04926819972759348</v>
+        <v>0.0248122154555022</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.005039977760046984</v>
+        <v>-0.001947888161262651</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
@@ -4270,106 +4270,106 @@
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.07792886582258754</v>
+        <v>-0.02201427702097172</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.06962480090931868</v>
+        <v>-0.003999355536396325</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.04420912527980097</v>
+        <v>0.04523830009887849</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.07411415406786084</v>
+        <v>-0.004322490834745348</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.01999267047805387</v>
+        <v>0.002922579139684644</v>
       </c>
       <c r="EW7" t="n">
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.04544303651976302</v>
+        <v>-0.08597809563931263</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.03055265639138256</v>
+        <v>0.06716674268518059</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.001401414207885027</v>
+        <v>0.01106257880713301</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.005922891480010188</v>
+        <v>-0.003702887973770427</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.05300645436388881</v>
+        <v>-0.01190893605911458</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0.02600230782696497</v>
+        <v>0.005787431281608918</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.04156660549208569</v>
+        <v>0.04031122054409991</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.01954583202175084</v>
+        <v>-0.005979674516352942</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.0671931548172862</v>
+        <v>0.008872504594461421</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.03279686780219747</v>
+        <v>0.08941997955920655</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.02251160493409102</v>
+        <v>-0.1500360639297619</v>
       </c>
       <c r="FU7" t="n">
         <v>-0</v>
@@ -4378,34 +4378,34 @@
         <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0.000957428261148275</v>
+        <v>0.0458909118055434</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.04472394309577911</v>
+        <v>-0.04329358643914936</v>
       </c>
       <c r="GA7" t="n">
         <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.02772620629182646</v>
+        <v>0.01311562561776401</v>
       </c>
       <c r="GC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.01457096976144628</v>
+        <v>-0.02030258838669824</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4416,25 +4416,25 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03192127769382491</v>
+        <v>0.3282765022464724</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.002167365275056068</v>
+        <v>0.04688595300174128</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.04521285125905532</v>
+        <v>-0.212833630126667</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006559247809877196</v>
+        <v>0.1201171253069738</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,25 +4452,25 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.001678411740210573</v>
+        <v>-0.01299666956867715</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.00434144158194434</v>
+        <v>-0.02269212102712352</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.006187777515251562</v>
+        <v>0.1084764540008693</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -4479,40 +4479,40 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.002109380022389783</v>
+        <v>-0.05641854982740856</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001956727998272055</v>
+        <v>0.007340775682566253</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" t="n">
         <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01090818566595523</v>
+        <v>-0.1510934216258602</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01728762133353848</v>
+        <v>-0.2446040903166794</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.00476903484194214</v>
+        <v>0.05387935427316615</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
@@ -4521,10 +4521,10 @@
         <v>-0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.0002124462788537997</v>
+        <v>0.1294772287423899</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
@@ -4533,43 +4533,43 @@
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.008133374310037961</v>
+        <v>0.06905747131326588</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.005911279271414144</v>
+        <v>-0.04846438666144737</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0448942934773507</v>
+        <v>0.4716555296361973</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.006545144825219282</v>
+        <v>-0.2401265988337931</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.0123523625939461</v>
+        <v>-0.100420547432718</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB8" t="n">
         <v>0</v>
@@ -4578,52 +4578,52 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.01004170634235087</v>
+        <v>0.023560872110441</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.007217207811560774</v>
+        <v>-0.0008599178239553521</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.02451868129229942</v>
+        <v>-0.06896306597515493</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.03312393375153382</v>
+        <v>0.05125532876635065</v>
       </c>
       <c r="BN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO8" t="n">
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0132077058663768</v>
+        <v>0.09851822245669578</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-0.0003798049843237398</v>
+        <v>0.120041184093289</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.008799870562731732</v>
+        <v>0.4245479936832323</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,43 +4641,43 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.004505915978035938</v>
+        <v>0.001552736869212203</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.004847558917821859</v>
+        <v>-0.0981627505836854</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.006277630277000806</v>
+        <v>-0.1615381970254513</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0009887771333671868</v>
+        <v>-0.05984525423610144</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.01715867296927413</v>
+        <v>0.12682820234121</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL8" t="n">
         <v>-0</v>
@@ -4686,22 +4686,22 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0009310031713916565</v>
+        <v>-0.1783585471160043</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
         <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.009654355918047926</v>
+        <v>0.03142178695032172</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.00732665944015741</v>
+        <v>0.02402303912539432</v>
       </c>
       <c r="CS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT8" t="n">
         <v>0</v>
@@ -4713,22 +4713,22 @@
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.001724683164835119</v>
+        <v>-0.1382527761462963</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.002521822765494476</v>
+        <v>-0.04778921621761726</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.01553093123055343</v>
+        <v>0.1362112766089477</v>
       </c>
       <c r="DB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC8" t="n">
         <v>0</v>
@@ -4737,49 +4737,49 @@
         <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.004851043593774697</v>
+        <v>-0.1634310873663916</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.00958581348764566</v>
+        <v>-0.1553716097347533</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0114280054080177</v>
+        <v>0.09108448849597787</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.004061869758191452</v>
+        <v>-0.1081218605885379</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.02140611915623683</v>
+        <v>0.04074601183651255</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0.007521507763303464</v>
+        <v>0.03466663279584377</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
@@ -4794,25 +4794,25 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.008140049058601013</v>
+        <v>0.02180429308596697</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.008523572928944484</v>
+        <v>0.03208913569974944</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.004120462242513867</v>
+        <v>0.1599006792127356</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>-0</v>
@@ -4821,19 +4821,19 @@
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.001196280578368076</v>
+        <v>0.01611472986412271</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>-0.008022228321931675</v>
+        <v>-0.107759913101593</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.009987676074284231</v>
+        <v>0.05874335745969072</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
@@ -4845,10 +4845,10 @@
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.007600122381612946</v>
+        <v>-0.06946027257727681</v>
       </c>
       <c r="EQ8" t="n">
         <v>-0</v>
@@ -4857,16 +4857,16 @@
         <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.001654858908959142</v>
+        <v>-0.2938210612126899</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.01375371802632202</v>
+        <v>0.07969576586454818</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
         <v>0</v>
@@ -4875,22 +4875,22 @@
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.0009650320346089882</v>
+        <v>-0.1699494831445836</v>
       </c>
       <c r="EZ8" t="n">
         <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.002647621003954301</v>
+        <v>-0.08804191935296612</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.01766570558997187</v>
+        <v>0.1079791632002424</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>-0</v>
@@ -4899,10 +4899,10 @@
         <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.003273546861829438</v>
+        <v>-0.1726010838064041</v>
       </c>
       <c r="FI8" t="n">
         <v>0</v>
@@ -4911,25 +4911,25 @@
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.01844461567922705</v>
+        <v>0.131266374262836</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.006966312777965753</v>
+        <v>0.1179380116189638</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.003124908442826153</v>
+        <v>0.04678962282315974</v>
       </c>
       <c r="FR8" t="n">
         <v>0</v>
@@ -4938,43 +4938,43 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.001648633314820085</v>
+        <v>-0.03304235230219994</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.02360035712904761</v>
+        <v>-0.05895583643394655</v>
       </c>
       <c r="FV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.01997523112673393</v>
+        <v>-0.01822945266080258</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.002452396013568039</v>
+        <v>0.1371987065759436</v>
       </c>
       <c r="GE8" t="n">
         <v>0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>0</v>
@@ -4985,43 +4985,43 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1786855064131685</v>
+        <v>0.2072803562995653</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09404937713504735</v>
+        <v>-0.1132313398094823</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0004866961718810459</v>
+        <v>-0.01893540739138403</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04623302011231223</v>
+        <v>0.07667612441732084</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01212222872717321</v>
+        <v>0.01971207900326096</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.004374545655461683</v>
+        <v>-0.01555544149356997</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5036,28 +5036,28 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03788838917472091</v>
+        <v>0.0551826003527795</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.01291895784616135</v>
+        <v>-0.01086740747440287</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02974823766857936</v>
+        <v>-0.0221870024791371</v>
       </c>
       <c r="X9" t="n">
         <v>-0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,43 +5066,43 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.03849612938329772</v>
+        <v>-0.04130642576518684</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.009085871771403166</v>
+        <v>-0.09900868117114114</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.005198937713703968</v>
+        <v>-0.07902089161137943</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.02186071217890684</v>
+        <v>0.0976774637119036</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.04064910678920006</v>
+        <v>-0.07118060459986275</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.04287241658473091</v>
+        <v>0.06632255555131453</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5111,31 +5111,31 @@
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.2846046527907125</v>
+        <v>0.2528552194251835</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.01477066526463485</v>
+        <v>-0.1152057581272824</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1355640065061368</v>
+        <v>-0.1381283281474455</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
         <v>-0</v>
@@ -5147,16 +5147,16 @@
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.005099538214369825</v>
+        <v>-0.001833253468769686</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.02181366450197863</v>
+        <v>-0.002327724005521558</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.03848436057374957</v>
+        <v>0.009340073029398228</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0683596626134816</v>
+        <v>0.003536373186714694</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.04361471875991176</v>
+        <v>0.05409796740428353</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.07954089695326336</v>
+        <v>0.08175085963247611</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,25 +5201,25 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1365737988685334</v>
+        <v>0.2270780733480276</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.02454381925620269</v>
+        <v>-0.1040979234363812</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.06315297373617226</v>
+        <v>-0.03088820828930457</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
         <v>0</v>
@@ -5228,16 +5228,16 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.04561318330148684</v>
+        <v>-0.08430023847970326</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.01836937340616224</v>
+        <v>0.09957855140064399</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.02312977860730333</v>
+        <v>-0.008530517739970029</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
@@ -5249,25 +5249,25 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.02625704034022857</v>
+        <v>-0.0832167329397261</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.09904436072858433</v>
+        <v>0.09394197904538043</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.09226866179803805</v>
+        <v>-0.00763595167033674</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5282,16 +5282,16 @@
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.03828204939013863</v>
+        <v>-0.088820713066082</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.02781754453525</v>
+        <v>0.1019297963147829</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.0147256493600479</v>
+        <v>0.004521894470999521</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
@@ -5303,28 +5303,28 @@
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.03518678049167209</v>
+        <v>-0.09523414979698987</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.01670480755888969</v>
+        <v>0.02851185568960685</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.01399179554407953</v>
+        <v>-0.02135402418006967</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,214 +5336,214 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.04097273447392315</v>
+        <v>-0.07745061720886894</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.03402536907116584</v>
+        <v>0.03148597954391326</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.01843879346187738</v>
+        <v>0.001865375683251342</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0279539008569438</v>
+        <v>0.02662681528011088</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.02108849109361009</v>
+        <v>-0.09780609060072142</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.009021710356036571</v>
+        <v>0.06096564681095101</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.01935939362592573</v>
+        <v>-0.02009228234550435</v>
       </c>
       <c r="EH9" t="n">
         <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.02419663762447629</v>
+        <v>0.06455178137788703</v>
       </c>
       <c r="EJ9" t="n">
-        <v>5.610298257030234e-05</v>
+        <v>0.01226643520037811</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.06285643367160533</v>
+        <v>-0.04544320857562613</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.00140029512026229</v>
+        <v>0.08005939485909183</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.02176613964548681</v>
+        <v>-0.03823316159235294</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.04157068286013278</v>
+        <v>-0.1050877501690738</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.02431491926729434</v>
+        <v>0.1109081424652029</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.01550907401484989</v>
+        <v>-0.01234337307787906</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.01835015660977493</v>
+        <v>-0.06429735955251424</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.04059958159768784</v>
+        <v>0.008455297139893255</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.003567163735715632</v>
+        <v>0.05502828232761914</v>
       </c>
       <c r="FL9" t="n">
         <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
         <v>0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
         <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.01956596056434734</v>
+        <v>-0.0270541522598121</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.006726939796592385</v>
+        <v>0.1278736154232149</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0558540920820175</v>
+        <v>-0.005514161072732818</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.03936570386150628</v>
+        <v>-0.05754290497178073</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.04686902614062403</v>
+        <v>0.03768901595031929</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>-0</v>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.09210470742889779</v>
+        <v>0.3333843544733356</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,10 +5563,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01347309578128683</v>
+        <v>0.05911011980484893</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1174093184459797</v>
+        <v>-0.2910017092167267</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -5578,10 +5578,10 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02851388526764089</v>
+        <v>0.1842200933909829</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
@@ -5590,16 +5590,16 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.003202288833256647</v>
+        <v>-0.01351390223201413</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0290507492276012</v>
+        <v>-0.08004787515426101</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -5608,61 +5608,61 @@
         <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.007126248783668201</v>
+        <v>0.1437260623844258</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.02732653118966045</v>
+        <v>-0.1267960448015014</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.0009183027925723772</v>
+        <v>0.02415409956026806</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0202770066918281</v>
+        <v>-0.06757515216665978</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.03225104004230271</v>
+        <v>-0.3490005660986713</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.005288528062354792</v>
+        <v>-0.131785759562717</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02298562850916325</v>
+        <v>0.1801915509764161</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
@@ -5671,13 +5671,13 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.007578445753080643</v>
+        <v>0.1064173938916511</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.0266501480552579</v>
+        <v>-0.1988540206962776</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
@@ -5686,22 +5686,22 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1066602616663326</v>
+        <v>0.7581730163328849</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.03028376030774575</v>
+        <v>-0.240519048912271</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.07082374029344093</v>
+        <v>-0.1857609832285469</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -5710,13 +5710,13 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0227608417246574</v>
+        <v>-0.06775821283324417</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,91 +5725,91 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.01226777839459723</v>
+        <v>-0.1470369149392562</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.0311657199056336</v>
+        <v>-0.1375329777232686</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.04739430713255471</v>
+        <v>0.05868968412822191</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>-0.002702328582188806</v>
+        <v>0.1195583005612086</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01244879839145795</v>
+        <v>0.06732986898746859</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.04805344107747205</v>
+        <v>0.4635233265868829</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.03251924546652708</v>
+        <v>-0.05599758331957543</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.03093609677553102</v>
+        <v>-0.2266556571273781</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.01783943910342767</v>
+        <v>-0.1836728462335205</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.007980343735665554</v>
+        <v>0.0003437714047571639</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.04149341551779026</v>
+        <v>0.1777795199547939</v>
       </c>
       <c r="CJ10" t="n">
         <v>-0</v>
@@ -5818,25 +5818,25 @@
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.0003697603242616283</v>
+        <v>-0.3162721068273555</v>
       </c>
       <c r="CO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.01080122900923652</v>
+        <v>0.4789604669790899</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.02319427071718367</v>
+        <v>0.3164923740524153</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
@@ -5848,22 +5848,22 @@
         <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.01112362524141081</v>
+        <v>-0.1622914437877174</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.004628190334300436</v>
+        <v>-0.02804688918665574</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0431654212000912</v>
+        <v>0.1538888975590849</v>
       </c>
       <c r="DB10" t="n">
         <v>0</v>
@@ -5878,46 +5878,46 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.009714807367917787</v>
+        <v>-0.02617588073103629</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01741122598315361</v>
+        <v>-0.14484298163632</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.002990208032855752</v>
+        <v>0.02556868180146237</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.008028022663026995</v>
+        <v>-0.06734458062803089</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.02972949716014356</v>
+        <v>-0.05255107562599397</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.004252059201653312</v>
+        <v>0.1572456348259931</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
@@ -5932,25 +5932,25 @@
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.01265400618242716</v>
+        <v>0.06877025755220999</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.01476516189036527</v>
+        <v>-0.03461893278483121</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.01054565357211986</v>
+        <v>0.08618488514867551</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
@@ -5959,19 +5959,19 @@
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.005633143947147426</v>
+        <v>-0.05171685838307127</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
         <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.001066540610547093</v>
+        <v>-0.07552267781221189</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.04277678075998081</v>
+        <v>-0.007883499908709096</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
@@ -5980,13 +5980,13 @@
         <v>0</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.009695984453779458</v>
+        <v>-0.044442950691788</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
@@ -5995,37 +5995,37 @@
         <v>0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.0231305366115153</v>
+        <v>-0.1769428251941141</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.06209071167172104</v>
+        <v>0.09684121211331802</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.01060744151932904</v>
+        <v>-0.194269251137249</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.006460767158145609</v>
+        <v>-0.05909717515547016</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.04328426184087002</v>
+        <v>0.148741981713384</v>
       </c>
       <c r="FD10" t="n">
         <v>-0</v>
@@ -6040,19 +6040,19 @@
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.02761044702433122</v>
+        <v>-0.1796166302837107</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.0005993825475118104</v>
+        <v>0.164688729881947</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.007172516400954189</v>
+        <v>-0.08926223097470794</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
@@ -6067,34 +6067,34 @@
         <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0009129268856865214</v>
+        <v>0.0486330243473996</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0009157080170955358</v>
+        <v>0.01269122189506395</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0.009167428614215803</v>
+        <v>-0.004195265694135939</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.01239751276556495</v>
+        <v>-0.07968524517550477</v>
       </c>
       <c r="GA10" t="n">
         <v>0</v>
@@ -6103,16 +6103,16 @@
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.01261081818820498</v>
+        <v>0.02101204961789779</v>
       </c>
       <c r="GE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
         <v>0</v>
@@ -6123,73 +6123,73 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3017656482574297</v>
+        <v>0.2183539451476497</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.07990930653393963</v>
+        <v>-0.08784651724961051</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.02654266565282948</v>
+        <v>-0.02669976072399244</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.08347348576049204</v>
+        <v>0.09256368865195201</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.006227333897861984</v>
+        <v>-0.008366293393501024</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.01555403073214295</v>
+        <v>-0.02519800934203897</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09093443021960643</v>
+        <v>0.03597822020275677</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.01874267695440963</v>
+        <v>-0.0191633078859368</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01589974757612766</v>
+        <v>-0.04848238453132938</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
@@ -6201,55 +6201,55 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.03869440976836925</v>
+        <v>-0.02364616462448322</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.01592635975434656</v>
+        <v>-0.06672735274123018</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.02295562794138831</v>
+        <v>-0.08482669189565932</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03316420104703968</v>
+        <v>0.09672731601102678</v>
       </c>
       <c r="AM11" t="n">
         <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.0551712126526865</v>
+        <v>-0.01496636747527096</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.05071571855858059</v>
+        <v>0.06902906317050309</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
@@ -6258,16 +6258,16 @@
         <v>-0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.3759742722037662</v>
+        <v>0.2600998482446124</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.01914177744079298</v>
+        <v>-0.03596167475866113</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.09262518626204748</v>
+        <v>-0.1210813579162695</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
@@ -6276,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
         <v>-0</v>
@@ -6285,16 +6285,16 @@
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.006142377567785751</v>
+        <v>-0.009255497649392135</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.03183730670170884</v>
+        <v>0.0007326529704474172</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.05135140265027405</v>
+        <v>-0.01332743472288633</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6303,31 +6303,31 @@
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.05467811713358755</v>
+        <v>-0.01288935888933821</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0454925134240363</v>
+        <v>0.0002766741090503657</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.1177224106244065</v>
+        <v>0.06481382805165756</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6339,19 +6339,19 @@
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1960066316380888</v>
+        <v>0.1873305495140359</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.02166843389483894</v>
+        <v>-0.09163820734764255</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0337049356269357</v>
+        <v>-0.02455882335296199</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6360,25 +6360,25 @@
         <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.08066729636694167</v>
+        <v>-0.09423190516313289</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.008972519369115433</v>
+        <v>0.06362472377938948</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.01535078414867847</v>
+        <v>0.01551393014464244</v>
       </c>
       <c r="CI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ11" t="n">
         <v>-0</v>
@@ -6387,58 +6387,58 @@
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.02215183954925417</v>
+        <v>-0.07794031967236188</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.06066607291819601</v>
+        <v>0.08953751782941237</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.09967332353897548</v>
+        <v>0.03781624145055152</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
         <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.07117243338240935</v>
+        <v>-0.09247519144274637</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.02248849534178899</v>
+        <v>0.06730108521059515</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.01489478581314506</v>
+        <v>0.01442014679096143</v>
       </c>
       <c r="DA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,22 +6447,22 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.003741794435929306</v>
+        <v>0.003112174815130873</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.01871409537674262</v>
+        <v>0.0150511781156988</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.03702391390006553</v>
+        <v>-0.03866478860418437</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL11" t="n">
         <v>0</v>
@@ -6474,151 +6474,151 @@
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.04885650802916838</v>
+        <v>-0.05791891649557802</v>
       </c>
       <c r="DP11" t="n">
         <v>0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.01446766111850815</v>
+        <v>-0.01176024178873872</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.03316953437169993</v>
+        <v>-0.007207854064189963</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0438489188304958</v>
+        <v>0.08393436212077429</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.001149955514790745</v>
+        <v>0.03594064270488417</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.05687772426192475</v>
+        <v>-0.07454503663860224</v>
       </c>
       <c r="EB11" t="n">
         <v>0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
         <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
         <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.06911683363151017</v>
+        <v>-0.0495870797112623</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.02299052186341357</v>
+        <v>0.05856435820876767</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.02988402928089696</v>
+        <v>0.01698095629039901</v>
       </c>
       <c r="EK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.05176796436357432</v>
+        <v>-0.03986683437926694</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.03111458654780713</v>
+        <v>0.05452924840971168</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.007250029016247001</v>
+        <v>-0.02660631516206833</v>
       </c>
       <c r="ET11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.07233281828392406</v>
+        <v>-0.0974779713734345</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.01625004158412825</v>
+        <v>0.07255416195614338</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.006410697439343241</v>
+        <v>-0.00166481132365308</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.009991464683040772</v>
+        <v>-0.02143477387932599</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.0117035573966711</v>
+        <v>0.04062153230752507</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.03400145871863834</v>
+        <v>-0.03925011179581708</v>
       </c>
       <c r="FL11" t="n">
         <v>-0</v>
@@ -6630,28 +6630,28 @@
         <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.001742342230571659</v>
+        <v>0.00914928195777647</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.002632620354687212</v>
+        <v>0.08788678793494081</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.003404350071809533</v>
+        <v>-0.01157723687015044</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW11" t="n">
         <v>0</v>
@@ -6660,31 +6660,31 @@
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.01634329917391489</v>
+        <v>-0.07796487328060303</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0.03699785307823184</v>
+        <v>0.03672524783598674</v>
       </c>
       <c r="GC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF11" t="n">
         <v>0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3860685444695524</v>
+        <v>0.3647806793238299</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1141690800741555</v>
+        <v>-0.172036741715225</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08271188432472305</v>
+        <v>0.01968429395090859</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6719,22 +6719,22 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1829355616396811</v>
+        <v>0.2183298321620929</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.01446054530959619</v>
+        <v>-0.02217985210314379</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.04453142952883181</v>
+        <v>-0.002924705141801217</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -6743,52 +6743,52 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1369772785662917</v>
+        <v>0.1016377250136189</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.02982205587082784</v>
+        <v>-0.02922826636402784</v>
       </c>
       <c r="W12" t="n">
-        <v>0.07347206322869854</v>
+        <v>-0.0691903113895815</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1260752604204138</v>
+        <v>-0.06636456577642461</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.04687873967860352</v>
+        <v>-0.173719828905508</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.03123882427387175</v>
+        <v>-0.0373524129183398</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6797,19 +6797,19 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0517373757069514</v>
+        <v>0.1479810468036685</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.04693577510272039</v>
+        <v>-0.07966742889036647</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.02873920170596778</v>
+        <v>0.1138387768089732</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6827,16 +6827,16 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.4352448661264277</v>
+        <v>0.3695804843578664</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.003029365963111259</v>
+        <v>-0.152308901954658</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1354190088360794</v>
+        <v>-0.1137689097679482</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
@@ -6848,22 +6848,22 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.02836527991567364</v>
+        <v>-0.01617406426559779</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.03404178528994286</v>
+        <v>-0.02923407922887424</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1253338311084696</v>
+        <v>-0.02218312207148299</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,22 +6881,22 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.01864119223171074</v>
+        <v>-0.03116865778580338</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.04445658946713062</v>
+        <v>0.03884501496101608</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.05145281084716107</v>
+        <v>0.02711383900795365</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,49 +6908,49 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2604690935085517</v>
+        <v>0.327082976889236</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.02231307279963652</v>
+        <v>-0.1146176438750104</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.07943533834213067</v>
+        <v>-0.01424526978808908</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.09827690266432829</v>
+        <v>-0.1396795763294643</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.02618285090985644</v>
+        <v>0.1470726399942006</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.02315152757546453</v>
+        <v>-0.04254836521647105</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6962,19 +6962,19 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.05345134043065182</v>
+        <v>-0.1298057512778343</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.07476594241106028</v>
+        <v>0.2248686083792075</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.167076016087498</v>
+        <v>0.02927684884562921</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6989,22 +6989,22 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.09150580622032395</v>
+        <v>-0.1285504083555058</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.03576284586004064</v>
+        <v>0.1408212952413083</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.01998796279913451</v>
+        <v>-0.02884671728370796</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
@@ -7013,25 +7013,25 @@
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.04256947303042163</v>
+        <v>-0.03811654224551935</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.01581421298383295</v>
+        <v>0.01736056773571083</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0004951969159955818</v>
+        <v>0.005380772385159763</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7040,22 +7040,22 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.05204242744462474</v>
+        <v>-0.07924915251009387</v>
       </c>
       <c r="DP12" t="n">
         <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.005463698325473166</v>
+        <v>0.06638603440898624</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.06204460443714819</v>
+        <v>-0.01112876349694857</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
@@ -7070,76 +7070,76 @@
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.08895742217609767</v>
+        <v>-0.005933609110331424</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.0204191241031179</v>
+        <v>-0.09247220723306046</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.006132100995516686</v>
+        <v>0.1089573596793195</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.06172239568230441</v>
+        <v>-0.08750035412337751</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.03635916135260377</v>
+        <v>0.1098907892894518</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.03997454528862483</v>
+        <v>0.0115433616085429</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.07627387971790586</v>
+        <v>-0.08446253302355194</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0206473654388265</v>
+        <v>0.06189068000717168</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.03062252082218282</v>
+        <v>-0.03677841590866018</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7148,25 +7148,25 @@
         <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1025882726777533</v>
+        <v>-0.1546360374439853</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.04450534965843048</v>
+        <v>0.161990290820082</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.02725858841128379</v>
+        <v>-0.05172216921175717</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
@@ -7178,16 +7178,16 @@
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.007373691659527414</v>
+        <v>-0.1230854776103581</v>
       </c>
       <c r="FI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.06288626401431556</v>
+        <v>0.09742313101848125</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.04604291415433229</v>
+        <v>-0.004779892956332153</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,64 +7196,64 @@
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.01410257397447073</v>
+        <v>-0.01614694594528322</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.1281988544453152</v>
+        <v>-0.168954940891126</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.02382377109969946</v>
+        <v>-0.02410282736933757</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.04158371759998803</v>
+        <v>-0.1131176495357851</v>
       </c>
       <c r="GA12" t="n">
         <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.04610191740933486</v>
+        <v>0.08896809644111335</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7827,22 +7827,22 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1052658734163721</v>
+        <v>0.627422820536647</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.04320202057340328</v>
+        <v>0.06061191564797961</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.05905002278961895</v>
+        <v>-0.3559869063142942</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
@@ -7857,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.04295118699287189</v>
+        <v>0.4848470099800309</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -7866,13 +7866,13 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.02626478918343891</v>
+        <v>-0.07477875402112276</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.01779210163083662</v>
+        <v>-0.1248566387190366</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>-0</v>
@@ -7881,10 +7881,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.004315201574558581</v>
+        <v>0.1865836190134013</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -7893,16 +7893,16 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.02118477643181161</v>
+        <v>-0.1508150897546938</v>
       </c>
       <c r="X14" t="n">
-        <v>0.02208182202543177</v>
+        <v>-0.054449992586172</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>-0</v>
@@ -7911,34 +7911,34 @@
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.02178893815435579</v>
+        <v>-0.02451221587952385</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.02255643972430705</v>
+        <v>-0.3043818300567229</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.008955529374286314</v>
+        <v>-0.08725303996372012</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI14" t="n">
         <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01934415261992584</v>
+        <v>0.2047296173217211</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
@@ -7947,13 +7947,13 @@
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.01134245279903199</v>
+        <v>0.05375847318474691</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.02047164354368227</v>
+        <v>-0.18902297130363</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
         <v>-0</v>
@@ -7962,22 +7962,22 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.08397229367139974</v>
+        <v>0.8549474041771488</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.03965968528460088</v>
+        <v>-0.2276815909294671</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.0307696123454659</v>
+        <v>-0.3443997222646378</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -7986,13 +7986,13 @@
         <v>-0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC14" t="n">
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.03177258358605593</v>
+        <v>-0.06715582659037572</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -8001,13 +8001,13 @@
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.01930709527244431</v>
+        <v>-0.06485595659530104</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.01243948089378175</v>
+        <v>-0.06604753806436144</v>
       </c>
       <c r="BI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ14" t="n">
         <v>-0</v>
@@ -8016,37 +8016,37 @@
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.04010860812152438</v>
+        <v>0.0822693464709838</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.02954463615503292</v>
+        <v>0.1436962341524636</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.01416156279207613</v>
+        <v>0.07772264146023329</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.04674285588966193</v>
+        <v>0.5563287333754479</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
@@ -8055,40 +8055,40 @@
         <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.01788130102593049</v>
+        <v>-0.07118081701521775</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.002134030280392688</v>
+        <v>-0.2323851639056316</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB14" t="n">
         <v>-0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
         <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.01621965963627819</v>
+        <v>-0.2479423257840932</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
         <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.005475792416234756</v>
+        <v>-0.02800688302190992</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.01726675697218584</v>
+        <v>0.1608544468760856</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
@@ -8100,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.005136498689521495</v>
+        <v>-0.3206695496005732</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
@@ -8109,13 +8109,13 @@
         <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.002702375558682941</v>
+        <v>0.1436771340074288</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0.02753638282070571</v>
+        <v>0.1762073625745528</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
         <v>0</v>
@@ -8124,25 +8124,25 @@
         <v>0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.0112676657924886</v>
+        <v>-0.2196143630494782</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
         <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.008010826526126556</v>
+        <v>-0.0466529040804157</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.022009830323133</v>
+        <v>0.1646349066419909</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
         <v>-0</v>
@@ -8151,76 +8151,76 @@
         <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.004415211012725574</v>
+        <v>-0.04056075903832509</v>
       </c>
       <c r="DG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.02306287208739509</v>
+        <v>-0.2390961412322847</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0.00406529454022137</v>
+        <v>0.005237428461781487</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
       </c>
       <c r="DL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.01511276425078155</v>
+        <v>-0.06403660509094541</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.0104815703175914</v>
+        <v>-0.05251297355714121</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0.01640995735574316</v>
+        <v>0.02654311202393523</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW14" t="n">
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.001985719039636225</v>
+        <v>0.1552989774217814</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
         <v>-0</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.02253200220825065</v>
+        <v>-0.04428079943792719</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0.01452478347826923</v>
+        <v>0.05495848003892043</v>
       </c>
       <c r="EC14" t="n">
         <v>-0</v>
@@ -8232,10 +8232,10 @@
         <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.009558445313801806</v>
+        <v>-0.0548734780467573</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
@@ -8244,13 +8244,13 @@
         <v>0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.005821113327950961</v>
+        <v>-0.1350478032104411</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.01807824704006479</v>
+        <v>0.06551998943514274</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>0</v>
@@ -8259,52 +8259,52 @@
         <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.003430035122489143</v>
+        <v>-0.1124493129546077</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
         <v>0</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.01151076542301022</v>
+        <v>-0.1804588040648966</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.01703347142483065</v>
+        <v>0.1325432674203112</v>
       </c>
       <c r="EU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
         <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.007987245776195473</v>
+        <v>-0.2611165978457194</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
         <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.005474481293517712</v>
+        <v>-0.07421597977614532</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.02218428055851368</v>
+        <v>0.1393396736848286</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
@@ -8313,82 +8313,82 @@
         <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.0161118348492827</v>
+        <v>-0.2070471483929382</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.03139741915767542</v>
+        <v>0.08820371317209454</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.02060621513307019</v>
+        <v>0.2355773998782035</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.002414092888160417</v>
+        <v>-0.02774485721425285</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.00048274181441153</v>
+        <v>0.0007724081856934323</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.008386938207461912</v>
+        <v>0.1548384933794067</v>
       </c>
       <c r="FV14" t="n">
         <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.01601264112464079</v>
+        <v>-0.1212523038078352</v>
       </c>
       <c r="GA14" t="n">
         <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0.01796211548304342</v>
+        <v>0.04147103644037487</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
         <v>0</v>
@@ -8396,28 +8396,28 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.08973733290996719</v>
+        <v>0.2077414505562488</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" t="n">
         <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.04363036533815026</v>
+        <v>0.01466234705374211</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.02156490498913307</v>
+        <v>-0.1077644325869491</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8426,34 +8426,34 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.03875571495573658</v>
+        <v>0.1794941332711215</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.03113179646541618</v>
+        <v>-0.02753071641080561</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.006479027623837866</v>
+        <v>-0.04495021081227519</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.006638853685983463</v>
+        <v>0.06180007958870848</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
@@ -8462,25 +8462,25 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.006616592756181581</v>
+        <v>-0.0558993875343902</v>
       </c>
       <c r="X15" t="n">
-        <v>0.01804225124850013</v>
+        <v>-0.02169353517665368</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.01810194689673993</v>
+        <v>-0.03144323551534938</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -8489,25 +8489,25 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.02277404962828885</v>
+        <v>-0.1064793166329098</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.007477851005114849</v>
+        <v>-0.04613413275717124</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.01467252895541128</v>
+        <v>0.06097964293644918</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
@@ -8516,37 +8516,37 @@
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.01457688889906194</v>
+        <v>0.01991828404009555</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.01261926141194078</v>
+        <v>-0.07216822196090436</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS15" t="n">
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.07458258276590379</v>
+        <v>0.2432388761723343</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.02270858578158457</v>
+        <v>-0.1050297328403207</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.005921112505210411</v>
+        <v>-0.09223632430093449</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -8561,7 +8561,7 @@
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.02902540495401127</v>
+        <v>-0.01399390515758598</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -8570,37 +8570,37 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.02440380830372408</v>
+        <v>-0.02071822565696174</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.01810430359439813</v>
+        <v>-0.04481183372135537</v>
       </c>
       <c r="BI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.04438539492627638</v>
+        <v>0.02026315752943795</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.02128943147858666</v>
+        <v>0.0699021580394064</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.01175582963469083</v>
+        <v>0.05807575369095936</v>
       </c>
       <c r="BR15" t="n">
         <v>-0</v>
@@ -8609,13 +8609,13 @@
         <v>0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.03760482512473504</v>
+        <v>0.1619083268834182</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
@@ -8624,16 +8624,16 @@
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.009207733777462635</v>
+        <v>-0.03846608167488708</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.01177033560236127</v>
+        <v>-0.07636058453363764</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
         <v>-0</v>
@@ -8642,22 +8642,22 @@
         <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.01113963544823329</v>
+        <v>-0.06851210580353395</v>
       </c>
       <c r="CF15" t="n">
         <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.008540381151450074</v>
+        <v>0.002226543794065762</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.009504973902215511</v>
+        <v>0.06562853534023264</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
@@ -8669,7 +8669,7 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.007565671789103549</v>
+        <v>-0.07212853004235267</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
@@ -8678,13 +8678,13 @@
         <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.00478063190907632</v>
+        <v>0.1004584927622055</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.01170301908861326</v>
+        <v>0.03650349465188414</v>
       </c>
       <c r="CS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT15" t="n">
         <v>-0</v>
@@ -8696,25 +8696,25 @@
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.006111028065611183</v>
+        <v>-0.06248877815009718</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.007956574682539366</v>
+        <v>-0.003929736350940091</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.01165319662273927</v>
+        <v>0.06837923266734859</v>
       </c>
       <c r="DB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
         <v>0</v>
@@ -8723,19 +8723,19 @@
         <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.008646543992966443</v>
+        <v>-0.03093544367386237</v>
       </c>
       <c r="DG15" t="n">
         <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.000661436020803211</v>
+        <v>-0.01243639979336099</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.003792270102109945</v>
+        <v>-0.01681630782781365</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
@@ -8744,31 +8744,31 @@
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.01474252436542887</v>
+        <v>-0.02629908806474939</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ15" t="n">
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.01933505821069114</v>
+        <v>-0.01482057690703066</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0.02131939216751958</v>
+        <v>-0.02146890654326647</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>-0</v>
@@ -8777,25 +8777,25 @@
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.0003051787991176317</v>
+        <v>0.03102927730278724</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.03126446484648008</v>
+        <v>-0.01044282629403498</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0.02569133796986356</v>
+        <v>0.02663036916940175</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
         <v>-0</v>
@@ -8804,79 +8804,79 @@
         <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.004783702941119086</v>
+        <v>-0.02033096619267932</v>
       </c>
       <c r="EH15" t="n">
         <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.006898259031043298</v>
+        <v>-0.02586847692215741</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.0016330287825996</v>
+        <v>0.03588493470202741</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.004532262027226124</v>
+        <v>-0.0379261295103732</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.0005377438406086963</v>
+        <v>-0.02783907988881224</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.01839370892917774</v>
+        <v>0.04457929896783316</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
         <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.004578271558871831</v>
+        <v>-0.07014806052570631</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.007737370836684438</v>
+        <v>-0.008723343313503471</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.01527916163317275</v>
+        <v>0.05111681997350929</v>
       </c>
       <c r="FD15" t="n">
         <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
         <v>-0</v>
@@ -8885,7 +8885,7 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.007607065827906051</v>
+        <v>-0.062732692020456</v>
       </c>
       <c r="FI15" t="n">
         <v>0</v>
@@ -8894,67 +8894,67 @@
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.03354914501259099</v>
+        <v>0.02253889683855139</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.01303743320966156</v>
+        <v>0.04711148695033097</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.002179299737852478</v>
+        <v>-0.01556740577559344</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS15" t="n">
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.000401249693616723</v>
+        <v>-0.0007360968758035229</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.003348842198980361</v>
+        <v>0.0483029259662929</v>
       </c>
       <c r="FV15" t="n">
         <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.02228688270709073</v>
+        <v>-0.04257255475824707</v>
       </c>
       <c r="GA15" t="n">
         <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.01637251541976336</v>
+        <v>0.04395152204113223</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
         <v>0</v>
@@ -9537,127 +9537,127 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3187051246916599</v>
+        <v>0.3551459068231119</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1489492520515811</v>
+        <v>-0.06624780114624799</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.09002751817248469</v>
+        <v>0.01098429745012845</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0622754085585477</v>
+        <v>-0.1016867037361101</v>
       </c>
       <c r="G17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>-0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1992021633405539</v>
+        <v>0.3409251365716396</v>
       </c>
       <c r="L17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1100223130379771</v>
+        <v>-0.1032063220192036</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.06384690876651669</v>
+        <v>-0.06126922043566328</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.03777947866233954</v>
+        <v>-0.03776431422260999</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.06748234503628472</v>
+        <v>0.04734494179420583</v>
       </c>
       <c r="U17" t="n">
         <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.01254594909241052</v>
+        <v>-0.08232009950528989</v>
       </c>
       <c r="W17" t="n">
-        <v>0.05182215268681091</v>
+        <v>-0.06073201395036021</v>
       </c>
       <c r="X17" t="n">
-        <v>0.04903665508515107</v>
+        <v>-0.03605285815306809</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.05591451940330632</v>
+        <v>-0.02133804096339007</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.04098066803660044</v>
+        <v>-0.1560318573565459</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.0113363782505748</v>
+        <v>-0.1148470254943638</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.01064786618755916</v>
+        <v>-0.04483845874131912</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.0004988108534246238</v>
+        <v>0.1068143413943105</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.02780742572324407</v>
+        <v>-0.05825390522548553</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.03672815432272445</v>
+        <v>0.05439081277967019</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.03421535914898376</v>
+        <v>-0.08972461437830465</v>
       </c>
       <c r="AQ17" t="n">
         <v>-0</v>
@@ -9666,25 +9666,25 @@
         <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.3203659829527116</v>
+        <v>0.3335868263825847</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>-0.0235898126052109</v>
+        <v>-0.009629259157114704</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.02984768583685589</v>
+        <v>-0.08780535925609508</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.02106020949174865</v>
+        <v>-0.09812328642952726</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -9696,103 +9696,103 @@
         <v>-0</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>-0.001072429440116345</v>
+        <v>-0.01140236750930894</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.02268530580535243</v>
+        <v>-0.06695445276446872</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.1044271899895412</v>
+        <v>-0.05139082285314105</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.0501200693083438</v>
+        <v>-0.0193104478582178</v>
       </c>
       <c r="BI17" t="n">
         <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.0592966882250069</v>
+        <v>0.02219673109581477</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.06457274857217001</v>
+        <v>0.002232439171185603</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.06362005606816112</v>
+        <v>0.08692222162543835</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.01862661953836153</v>
+        <v>0.01729389730064205</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.152904167159655</v>
+        <v>0.2021413850493318</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.03566426065558426</v>
+        <v>-0.03783706356007563</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.009301953566094579</v>
+        <v>-0.02168645206373425</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.03284267381300353</v>
+        <v>-0.08911401918887189</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
         <v>-0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.061904795409631</v>
+        <v>-0.09791737837251817</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.01143126725340684</v>
+        <v>0.03225610680804188</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.004601576058983013</v>
+        <v>0.01974887851725612</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.03282588123079866</v>
+        <v>0.0362721956170256</v>
       </c>
       <c r="CJ17" t="n">
         <v>-0</v>
@@ -9801,28 +9801,28 @@
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.02433470009147189</v>
+        <v>-0.1016975543828742</v>
       </c>
       <c r="CO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.09528500233630727</v>
+        <v>0.08915633568965595</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.06538539023569021</v>
+        <v>0.1217066319068705</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.07160432678532314</v>
+        <v>0.08301250285341864</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
         <v>-0</v>
@@ -9831,22 +9831,22 @@
         <v>0</v>
       </c>
       <c r="CV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.05000253652223097</v>
+        <v>-0.09174127876333839</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.03351915909049587</v>
+        <v>0.02623950052228598</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.006271334416042406</v>
+        <v>0.01432238616037525</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.04319125901262801</v>
+        <v>0.03659182256535285</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
@@ -9861,46 +9861,46 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.001289946644931425</v>
+        <v>-0.02671024991865038</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.0591172678738161</v>
+        <v>-0.04319015153530167</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.004797224275910277</v>
+        <v>0.1105160589223386</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.005229672910767832</v>
+        <v>-0.009201923717437098</v>
       </c>
       <c r="DK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
         <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.0254965042945452</v>
+        <v>-0.08322142236751776</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.05324006702549526</v>
+        <v>0.03760436146061279</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.003712847301586662</v>
+        <v>-0.007618156034576174</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.008459506739143901</v>
+        <v>0.005632129299275784</v>
       </c>
       <c r="DT17" t="n">
         <v>0</v>
@@ -9909,196 +9909,196 @@
         <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.01337753817993134</v>
+        <v>0.06467366230099063</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.004357915243516064</v>
+        <v>0.008505927472670033</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.05459072035472773</v>
+        <v>-0.00783106266820404</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.007400929234524437</v>
+        <v>0.02133215047088441</v>
       </c>
       <c r="EC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED17" t="n">
         <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.08162364597873287</v>
+        <v>-0.05904384290557171</v>
       </c>
       <c r="EH17" t="n">
         <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.05743983815859426</v>
+        <v>0.04834120355707774</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.04949568264106391</v>
+        <v>0.02638423161580142</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.006716332308729729</v>
+        <v>-0.001698439665190165</v>
       </c>
       <c r="EL17" t="n">
         <v>-0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.03908186418205387</v>
+        <v>-0.02245930463353922</v>
       </c>
       <c r="EQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.003316639717130403</v>
+        <v>0.01060469725224102</v>
       </c>
       <c r="ES17" t="n">
-        <v>-0.02262352136749712</v>
+        <v>0.006178462308005487</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.06565069416797123</v>
+        <v>0.08030112938705838</v>
       </c>
       <c r="EU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.04613182958976267</v>
+        <v>-0.1071331813787448</v>
       </c>
       <c r="EZ17" t="n">
         <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.0176625289103931</v>
+        <v>0.0227492879967365</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.006520506445012923</v>
+        <v>0.0106235942148288</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.03459328209596833</v>
+        <v>0.02900336782100998</v>
       </c>
       <c r="FD17" t="n">
         <v>0</v>
       </c>
       <c r="FE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.03965977904545533</v>
+        <v>-0.03317414728052074</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.05704261889428647</v>
+        <v>0.03266659876532933</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.00603480969582025</v>
+        <v>0.003943278395733587</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0.002910244989505028</v>
+        <v>0.02763113854297916</v>
       </c>
       <c r="FM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.01095635583721517</v>
+        <v>-0.09027110150367833</v>
       </c>
       <c r="FR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.01201145400328422</v>
+        <v>0.16897490766619</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.006632200171119691</v>
+        <v>-0.009100134241440631</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.01082056739895922</v>
+        <v>0.1117377186749091</v>
       </c>
       <c r="FV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.006014361215978115</v>
+        <v>-0.09272021558676033</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.04180194767149894</v>
+        <v>-0.07432465772898592</v>
       </c>
       <c r="GC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.01483391711139229</v>
+        <v>0.0006097985196584007</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -10675,7 +10675,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1507833027504652</v>
+        <v>0.5180481033177419</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -10684,10 +10684,10 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.07467417371888677</v>
+        <v>0.06147994282379924</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.06653412378738222</v>
+        <v>-0.209093573008236</v>
       </c>
       <c r="G19" t="n">
         <v>-0</v>
@@ -10702,7 +10702,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1094409410262945</v>
+        <v>0.643979264321317</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -10711,13 +10711,13 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.05496168156868961</v>
+        <v>-0.07181431967098559</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.03744628605783663</v>
+        <v>-0.1110065846545526</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>-0</v>
@@ -10726,10 +10726,10 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.01463975394307872</v>
+        <v>0.0825688503498333</v>
       </c>
       <c r="U19" t="n">
         <v>-0</v>
@@ -10738,25 +10738,25 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.02316929884272893</v>
+        <v>-0.06198560141531508</v>
       </c>
       <c r="X19" t="n">
-        <v>0.01937607019138276</v>
+        <v>0.04076128392298476</v>
       </c>
       <c r="Y19" t="n">
         <v>-0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.02767508389773804</v>
+        <v>0.01791058539452526</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -10765,13 +10765,13 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.02618960847411302</v>
+        <v>-0.1630568678752857</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.001143404702909475</v>
+        <v>-0.07516107783948249</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>-0</v>
@@ -10783,61 +10783,61 @@
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.02473386421884555</v>
+        <v>0.07902847171312587</v>
       </c>
       <c r="AM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.01232726247392478</v>
+        <v>0.0130707113805475</v>
       </c>
       <c r="AP19" t="n">
-        <v>-0.03229264730419328</v>
+        <v>-0.1534995418770378</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR19" t="n">
         <v>-0</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.09588355770063949</v>
+        <v>0.4745401595134287</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>-0.0324299892848357</v>
+        <v>-0.223957936144948</v>
       </c>
       <c r="AY19" t="n">
-        <v>-0.03545442588276625</v>
+        <v>-0.1342807609504265</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.02983601455468899</v>
+        <v>0.006898298446222749</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
@@ -10846,52 +10846,52 @@
         <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.04119053948865173</v>
+        <v>-0.05945762377877578</v>
       </c>
       <c r="BH19" t="n">
-        <v>-0.005366368448716368</v>
+        <v>-0.1059214426079688</v>
       </c>
       <c r="BI19" t="n">
         <v>-0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL19" t="n">
         <v>-0</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.04251893030799123</v>
+        <v>0.0813423821057223</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.02635054973591057</v>
+        <v>0.09997891046611389</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0.01899540148185775</v>
+        <v>-0.001708946803609338</v>
       </c>
       <c r="BR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
         <v>0</v>
       </c>
       <c r="BT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.05881871221633909</v>
+        <v>0.2973278672917199</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
@@ -10900,37 +10900,37 @@
         <v>0</v>
       </c>
       <c r="BY19" t="n">
-        <v>-0.02185609697105313</v>
+        <v>-0.08465652771461853</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0.005844403953537277</v>
+        <v>-0.08813786074675257</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC19" t="n">
         <v>-0</v>
       </c>
       <c r="CD19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE19" t="n">
-        <v>-0.0190709811779678</v>
+        <v>-0.1509462880393314</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG19" t="n">
         <v>-0</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.007675109732017718</v>
+        <v>0.03739010556203573</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.01547887986884864</v>
+        <v>0.06568594532480369</v>
       </c>
       <c r="CJ19" t="n">
         <v>-0</v>
@@ -10939,13 +10939,13 @@
         <v>0</v>
       </c>
       <c r="CL19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM19" t="n">
         <v>0</v>
       </c>
       <c r="CN19" t="n">
-        <v>0.001084650870710764</v>
+        <v>-0.2408495160815819</v>
       </c>
       <c r="CO19" t="n">
         <v>-0</v>
@@ -10954,13 +10954,13 @@
         <v>-0</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.01264115901661678</v>
+        <v>0.2585020257848481</v>
       </c>
       <c r="CR19" t="n">
-        <v>-0.02859485132024796</v>
+        <v>0.1242683961836985</v>
       </c>
       <c r="CS19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT19" t="n">
         <v>-0</v>
@@ -10972,19 +10972,19 @@
         <v>-0</v>
       </c>
       <c r="CW19" t="n">
-        <v>-0.01511049122574344</v>
+        <v>-0.1537191133321979</v>
       </c>
       <c r="CX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY19" t="n">
         <v>0</v>
       </c>
       <c r="CZ19" t="n">
-        <v>0.005730089539273469</v>
+        <v>-0.005172126432719299</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.02210293220111836</v>
+        <v>0.05930396982316762</v>
       </c>
       <c r="DB19" t="n">
         <v>0</v>
@@ -10999,19 +10999,19 @@
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.001469904406129279</v>
+        <v>0.002126596608247948</v>
       </c>
       <c r="DG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.01673648575857769</v>
+        <v>-0.0605692745775366</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.001094121716201831</v>
+        <v>0.01037031573494669</v>
       </c>
       <c r="DK19" t="n">
         <v>0</v>
@@ -11023,22 +11023,22 @@
         <v>0</v>
       </c>
       <c r="DN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>-0.01826452097067918</v>
+        <v>-0.08112097273615204</v>
       </c>
       <c r="DP19" t="n">
         <v>-0</v>
       </c>
       <c r="DQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>0.02629721780048799</v>
+        <v>-0.03961490702160498</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.0307774575120966</v>
+        <v>-0.005410691007561073</v>
       </c>
       <c r="DT19" t="n">
         <v>-0</v>
@@ -11047,25 +11047,25 @@
         <v>-0</v>
       </c>
       <c r="DV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW19" t="n">
         <v>-0</v>
       </c>
       <c r="DX19" t="n">
-        <v>0.0001847505999447847</v>
+        <v>0.05379098968229609</v>
       </c>
       <c r="DY19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ19" t="n">
         <v>0</v>
       </c>
       <c r="EA19" t="n">
-        <v>-0.02619775491746928</v>
+        <v>-0.05268054833391958</v>
       </c>
       <c r="EB19" t="n">
-        <v>-0.01772487370828326</v>
+        <v>-0.05592312843756012</v>
       </c>
       <c r="EC19" t="n">
         <v>-0</v>
@@ -11080,76 +11080,76 @@
         <v>0</v>
       </c>
       <c r="EG19" t="n">
-        <v>-0.01085945387854833</v>
+        <v>-0.03698881960208775</v>
       </c>
       <c r="EH19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.01774826038541308</v>
+        <v>-0.05929001476202606</v>
       </c>
       <c r="EK19" t="n">
-        <v>0.002849313117947491</v>
+        <v>0.02433424203969798</v>
       </c>
       <c r="EL19" t="n">
         <v>-0</v>
       </c>
       <c r="EM19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP19" t="n">
-        <v>-0.004220568307922598</v>
+        <v>-0.0693866785405625</v>
       </c>
       <c r="EQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES19" t="n">
-        <v>-0.01063190175657089</v>
+        <v>-0.03800474644069021</v>
       </c>
       <c r="ET19" t="n">
-        <v>-0.02310275477909809</v>
+        <v>-0.09810446638067608</v>
       </c>
       <c r="EU19" t="n">
         <v>-0</v>
       </c>
       <c r="EV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY19" t="n">
-        <v>-0.01192516502674933</v>
+        <v>-0.163350001726733</v>
       </c>
       <c r="EZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA19" t="n">
         <v>-0</v>
       </c>
       <c r="FB19" t="n">
-        <v>0.003181824698183061</v>
+        <v>0.007860646053425525</v>
       </c>
       <c r="FC19" t="n">
-        <v>0.0222865266786864</v>
+        <v>0.05230941185838079</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
         <v>0</v>
@@ -11158,37 +11158,37 @@
         <v>-0</v>
       </c>
       <c r="FG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH19" t="n">
-        <v>-0.01230257420660831</v>
+        <v>-0.1325234891259381</v>
       </c>
       <c r="FI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ19" t="n">
         <v>-0</v>
       </c>
       <c r="FK19" t="n">
-        <v>-0.0402899169604589</v>
+        <v>0.07938080095738352</v>
       </c>
       <c r="FL19" t="n">
-        <v>0.01520103024520643</v>
+        <v>0.1221670086556265</v>
       </c>
       <c r="FM19" t="n">
         <v>0</v>
       </c>
       <c r="FN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO19" t="n">
         <v>0</v>
       </c>
       <c r="FP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>-0.002409298342595829</v>
+        <v>-0.1169374370399837</v>
       </c>
       <c r="FR19" t="n">
         <v>-0</v>
@@ -11197,37 +11197,37 @@
         <v>-0</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.0003948844006530285</v>
+        <v>0.01811202582686371</v>
       </c>
       <c r="FU19" t="n">
-        <v>0.01479161714737616</v>
+        <v>0.07554990158658766</v>
       </c>
       <c r="FV19" t="n">
         <v>-0</v>
       </c>
       <c r="FW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>-0.01431095049276781</v>
+        <v>-0.07945850591444292</v>
       </c>
       <c r="GA19" t="n">
         <v>0</v>
       </c>
       <c r="GB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD19" t="n">
-        <v>-0.0228038178607163</v>
+        <v>-0.04679376899199307</v>
       </c>
       <c r="GE19" t="n">
         <v>-0</v>
